--- a/1차 Project(Flask,머신러닝)/2. 개발 스케줄.xlsx
+++ b/1차 Project(Flask,머신러닝)/2. 개발 스케줄.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BC9F624-EF05-46A7-A7D1-472A3BD66332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{56D9908A-E659-4F88-9DF6-CA68676A282A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{5636ACCF-BBBA-4970-9AF5-FF8110B379E7}"/>
   </bookViews>
@@ -56,6 +56,24 @@
     <t>DB 스키마 설계 및 적재</t>
   </si>
   <si>
+    <t>머신러닝</t>
+  </si>
+  <si>
+    <t>Time-Lag(시차) 변수 생성 및 상관성 분석</t>
+  </si>
+  <si>
+    <t>구별 가중치를 반영한 모델 학습</t>
+  </si>
+  <si>
+    <t>RandomForest, XGBoost, LightBGM 모델 비교 및 최적화</t>
+  </si>
+  <si>
+    <t>0~3일 후 환자 수 예측 수치 산출 및 오차 검증</t>
+  </si>
+  <si>
+    <t>API 연동을 위한 모델 직렬화(Pickle)</t>
+  </si>
+  <si>
     <t>UI</t>
   </si>
   <si>
@@ -77,34 +95,16 @@
     <t>데이터 연동 및 인터페이스 검수</t>
   </si>
   <si>
-    <t>머신러닝</t>
-  </si>
-  <si>
-    <t>Time-Lag(시차) 변수 생성 및 상관성 분석</t>
-  </si>
-  <si>
-    <t>구별 가중치를 반영한 모델 학습</t>
-  </si>
-  <si>
-    <t>RandomForest, XGBoost, LightBGM 모델 비교 및 최적화</t>
-  </si>
-  <si>
-    <t>0~3일 후 환자 수 예측 수치 산출 및 오차 검증</t>
-  </si>
-  <si>
-    <t>API 연동을 위한 모델 직렬화(Pickle)</t>
-  </si>
-  <si>
     <t>서비스</t>
   </si>
   <si>
+    <t>백엔드 API 서버 구축 및 모델 서빙 로직 구현</t>
+  </si>
+  <si>
     <t>위험 등급 및 사용자 행동요령 산출 로직</t>
   </si>
   <si>
-    <t>백엔드 API 서버 구축 및 모델 서빙 로직 구현</t>
-  </si>
-  <si>
-    <t>개인별 발병 확률 계산 알고리즘 적용</t>
+    <t>개인별 호흡기 증상 발현 확률 계산 알고리즘 적용</t>
   </si>
   <si>
     <t>위험 근거 시각화 및 회원 정보 관리 API</t>
@@ -126,7 +126,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="m\/d\(aaa\)"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,6 +193,26 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF56A31C"/>
+      <name val="Malgun Gothic"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFD9B3"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFBC82FF"/>
+      <name val="Malgun Gothic"/>
     </font>
   </fonts>
   <fills count="8">
@@ -264,7 +284,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -305,6 +325,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -313,32 +336,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -348,14 +377,14 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFEBD9FF"/>
+      <color rgb="FFBC82FF"/>
       <color rgb="FFD4F1BE"/>
       <color rgb="FFFFD9B3"/>
+      <color rgb="FF56A31C"/>
+      <color rgb="FFEBD9FF"/>
       <color rgb="FFEEB500"/>
       <color rgb="FFFAFAFA"/>
       <color rgb="FFF2F2F2"/>
-      <color rgb="FFBC82FF"/>
-      <color rgb="FF56A31C"/>
       <color rgb="FF92F547"/>
       <color rgb="FFE3EFFF"/>
     </mruColors>
@@ -677,34 +706,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="69.75" customHeight="1">
-      <c r="A1" s="19"/>
-      <c r="B1" s="19"/>
-      <c r="C1" s="20" t="s">
+      <c r="A1" s="21"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="20"/>
-      <c r="Z1" s="20"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
     </row>
     <row r="2" spans="1:26" ht="35.25" customHeight="1" thickBot="1">
       <c r="A2" s="10" t="s">
@@ -787,7 +816,7 @@
       </c>
     </row>
     <row r="3" spans="1:26" ht="35.25" customHeight="1" thickTop="1">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="23" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -819,7 +848,7 @@
       <c r="Z3" s="4"/>
     </row>
     <row r="4" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A4" s="21"/>
+      <c r="A4" s="23"/>
       <c r="B4" s="8" t="s">
         <v>5</v>
       </c>
@@ -849,7 +878,7 @@
       <c r="Z4" s="4"/>
     </row>
     <row r="5" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="19" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="9" t="s">
@@ -859,7 +888,7 @@
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="G5" s="17"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -881,7 +910,7 @@
       <c r="Z5" s="4"/>
     </row>
     <row r="6" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A6" s="22"/>
+      <c r="A6" s="19"/>
       <c r="B6" s="9" t="s">
         <v>8</v>
       </c>
@@ -889,9 +918,9 @@
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
-      <c r="G6" s="23"/>
+      <c r="G6" s="26"/>
       <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
+      <c r="I6" s="17"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -911,8 +940,8 @@
       <c r="Z6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A7" s="22"/>
-      <c r="B7" s="15" t="s">
+      <c r="A7" s="19"/>
+      <c r="B7" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="4"/>
@@ -920,9 +949,9 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="5"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="17"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
@@ -941,8 +970,8 @@
       <c r="Z7" s="4"/>
     </row>
     <row r="8" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A8" s="22"/>
-      <c r="B8" s="15" t="s">
+      <c r="A8" s="19"/>
+      <c r="B8" s="16" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="4"/>
@@ -951,9 +980,9 @@
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="5"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="17"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
@@ -971,8 +1000,8 @@
       <c r="Z8" s="4"/>
     </row>
     <row r="9" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A9" s="22"/>
-      <c r="B9" s="15" t="s">
+      <c r="A9" s="19"/>
+      <c r="B9" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="4"/>
@@ -982,9 +1011,9 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="5"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="17"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
@@ -1001,9 +1030,11 @@
       <c r="Z9" s="4"/>
     </row>
     <row r="10" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A10" s="22"/>
-      <c r="B10" s="15" t="s">
+      <c r="A10" s="24" t="s">
         <v>12</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -1012,10 +1043,10 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="5"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
@@ -1031,9 +1062,7 @@
       <c r="Z10" s="4"/>
     </row>
     <row r="11" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A11" s="17" t="s">
-        <v>13</v>
-      </c>
+      <c r="A11" s="24"/>
       <c r="B11" s="13" t="s">
         <v>14</v>
       </c>
@@ -1046,24 +1075,24 @@
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
       <c r="N11" s="6"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
-      <c r="S11" s="23"/>
-      <c r="T11" s="23"/>
-      <c r="U11" s="23"/>
-      <c r="V11" s="23"/>
-      <c r="W11" s="23"/>
-      <c r="X11" s="23"/>
-      <c r="Y11" s="23"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="17"/>
+      <c r="W11" s="17"/>
+      <c r="X11" s="17"/>
+      <c r="Y11" s="17"/>
       <c r="Z11" s="4"/>
     </row>
     <row r="12" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A12" s="17"/>
+      <c r="A12" s="24"/>
       <c r="B12" s="13" t="s">
         <v>15</v>
       </c>
@@ -1076,25 +1105,25 @@
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="6"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
       <c r="P12" s="6"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
-      <c r="T12" s="23"/>
-      <c r="U12" s="23"/>
-      <c r="V12" s="23"/>
-      <c r="W12" s="23"/>
-      <c r="X12" s="23"/>
-      <c r="Y12" s="23"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="17"/>
+      <c r="V12" s="17"/>
+      <c r="W12" s="17"/>
+      <c r="X12" s="17"/>
+      <c r="Y12" s="17"/>
       <c r="Z12" s="4"/>
     </row>
     <row r="13" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A13" s="17"/>
-      <c r="B13" s="16" t="s">
+      <c r="A13" s="24"/>
+      <c r="B13" s="13" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="4"/>
@@ -1106,25 +1135,25 @@
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
       <c r="Q13" s="6"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="23"/>
-      <c r="X13" s="23"/>
-      <c r="Y13" s="23"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="17"/>
+      <c r="V13" s="17"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="17"/>
+      <c r="Y13" s="17"/>
       <c r="Z13" s="4"/>
     </row>
     <row r="14" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A14" s="17"/>
-      <c r="B14" s="13" t="s">
+      <c r="A14" s="24"/>
+      <c r="B14" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="4"/>
@@ -1136,25 +1165,25 @@
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
       <c r="R14" s="6"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="23"/>
-      <c r="W14" s="23"/>
-      <c r="X14" s="23"/>
-      <c r="Y14" s="23"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="17"/>
+      <c r="U14" s="17"/>
+      <c r="V14" s="17"/>
+      <c r="W14" s="17"/>
+      <c r="X14" s="17"/>
+      <c r="Y14" s="17"/>
       <c r="Z14" s="4"/>
     </row>
     <row r="15" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A15" s="17"/>
-      <c r="B15" s="13" t="s">
+      <c r="A15" s="24"/>
+      <c r="B15" s="14" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="4"/>
@@ -1166,27 +1195,27 @@
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
       <c r="S15" s="6"/>
-      <c r="T15" s="23"/>
-      <c r="U15" s="23"/>
-      <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="23"/>
-      <c r="Y15" s="23"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="17"/>
+      <c r="V15" s="17"/>
+      <c r="W15" s="17"/>
+      <c r="X15" s="17"/>
+      <c r="Y15" s="17"/>
       <c r="Z15" s="4"/>
     </row>
     <row r="16" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C16" s="4"/>
@@ -1198,25 +1227,25 @@
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
-      <c r="S16" s="23"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="17"/>
       <c r="T16" s="7"/>
-      <c r="U16" s="23"/>
-      <c r="V16" s="23"/>
-      <c r="W16" s="23"/>
-      <c r="X16" s="23"/>
-      <c r="Y16" s="23"/>
+      <c r="U16" s="17"/>
+      <c r="V16" s="17"/>
+      <c r="W16" s="17"/>
+      <c r="X16" s="17"/>
+      <c r="Y16" s="17"/>
       <c r="Z16" s="4"/>
     </row>
     <row r="17" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A17" s="18"/>
-      <c r="B17" s="14" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="15" t="s">
         <v>21</v>
       </c>
       <c r="C17" s="4"/>
@@ -1228,25 +1257,25 @@
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
-      <c r="S17" s="23"/>
-      <c r="T17" s="23"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="17"/>
       <c r="U17" s="7"/>
-      <c r="V17" s="23"/>
-      <c r="W17" s="23"/>
-      <c r="X17" s="23"/>
-      <c r="Y17" s="23"/>
+      <c r="V17" s="17"/>
+      <c r="W17" s="17"/>
+      <c r="X17" s="17"/>
+      <c r="Y17" s="17"/>
       <c r="Z17" s="4"/>
     </row>
     <row r="18" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A18" s="18"/>
-      <c r="B18" s="14" t="s">
+      <c r="A18" s="20"/>
+      <c r="B18" s="15" t="s">
         <v>22</v>
       </c>
       <c r="C18" s="4"/>
@@ -1258,25 +1287,25 @@
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
-      <c r="S18" s="23"/>
-      <c r="T18" s="23"/>
-      <c r="U18" s="23"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="17"/>
+      <c r="U18" s="17"/>
       <c r="V18" s="7"/>
-      <c r="W18" s="23"/>
-      <c r="X18" s="23"/>
-      <c r="Y18" s="23"/>
+      <c r="W18" s="17"/>
+      <c r="X18" s="17"/>
+      <c r="Y18" s="17"/>
       <c r="Z18" s="4"/>
     </row>
     <row r="19" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A19" s="18"/>
-      <c r="B19" s="14" t="s">
+      <c r="A19" s="20"/>
+      <c r="B19" s="15" t="s">
         <v>23</v>
       </c>
       <c r="C19" s="4"/>
@@ -1288,25 +1317,25 @@
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
-      <c r="S19" s="23"/>
-      <c r="T19" s="23"/>
-      <c r="U19" s="23"/>
-      <c r="V19" s="23"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="17"/>
+      <c r="V19" s="17"/>
       <c r="W19" s="7"/>
-      <c r="X19" s="23"/>
-      <c r="Y19" s="23"/>
+      <c r="X19" s="17"/>
+      <c r="Y19" s="17"/>
       <c r="Z19" s="4"/>
     </row>
     <row r="20" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A20" s="18"/>
-      <c r="B20" s="14" t="s">
+      <c r="A20" s="20"/>
+      <c r="B20" s="15" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="4"/>
@@ -1318,20 +1347,20 @@
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
-      <c r="S20" s="23"/>
-      <c r="T20" s="23"/>
-      <c r="U20" s="23"/>
-      <c r="V20" s="23"/>
-      <c r="W20" s="23"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="17"/>
       <c r="X20" s="7"/>
-      <c r="Y20" s="23"/>
+      <c r="Y20" s="17"/>
       <c r="Z20" s="4"/>
     </row>
     <row r="21" spans="1:26" ht="35.25" customHeight="1">
@@ -1363,8 +1392,8 @@
       <c r="V21" s="4"/>
       <c r="W21" s="4"/>
       <c r="X21" s="4"/>
-      <c r="Y21" s="24"/>
-      <c r="Z21" s="24"/>
+      <c r="Y21" s="18"/>
+      <c r="Z21" s="18"/>
     </row>
     <row r="22" spans="1:26" hidden="1">
       <c r="A22" s="2"/>
@@ -1396,12 +1425,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A5:A10"/>
     <mergeCell ref="A16:A20"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:Z1"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A11:A15"/>
+    <mergeCell ref="A5:A9"/>
+    <mergeCell ref="A10:A15"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/1차 Project(Flask,머신러닝)/2. 개발 스케줄.xlsx
+++ b/1차 Project(Flask,머신러닝)/2. 개발 스케줄.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56D9908A-E659-4F88-9DF6-CA68676A282A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBDCE483-335A-419D-9551-FA971EFA1324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{5636ACCF-BBBA-4970-9AF5-FF8110B379E7}"/>
   </bookViews>
@@ -38,15 +38,24 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
-    <t>개발 스케줄</t>
-  </si>
-  <si>
     <t>분류</t>
   </si>
   <si>
     <t>항목</t>
   </si>
   <si>
+    <t>1주차</t>
+  </si>
+  <si>
+    <t>2주차</t>
+  </si>
+  <si>
+    <t>3주차</t>
+  </si>
+  <si>
+    <t>4주차</t>
+  </si>
+  <si>
     <t>데이터 전처리</t>
   </si>
   <si>
@@ -77,9 +86,6 @@
     <t>UI</t>
   </si>
   <si>
-    <t>개인 정보 입력 폼 UI 구현</t>
-  </si>
-  <si>
     <t>서울시 지도 인터페이스 및 구별 클릭 이벤트 구현</t>
   </si>
   <si>
@@ -111,12 +117,6 @@
   </si>
   <si>
     <t>사용자 맞춤형 예보 알림 및 데이터 예외 처리 로직</t>
-  </si>
-  <si>
-    <t>마무리</t>
-  </si>
-  <si>
-    <t>전체 기능 연동 및 최종 테스트</t>
   </si>
 </sst>
 </file>
@@ -126,7 +126,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="m\/d\(aaa\)"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,25 +180,12 @@
     </font>
     <font>
       <b/>
-      <sz val="30"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFEEB500"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF56A31C"/>
-      <name val="Malgun Gothic"/>
     </font>
     <font>
       <sz val="11"/>
@@ -214,8 +201,17 @@
       <color rgb="FFBC82FF"/>
       <name val="Malgun Gothic"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -252,14 +248,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -278,13 +268,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -315,58 +346,55 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -377,11 +405,11 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFEBD9FF"/>
+      <color rgb="FFD4F1BE"/>
       <color rgb="FFBC82FF"/>
-      <color rgb="FFD4F1BE"/>
       <color rgb="FFFFD9B3"/>
       <color rgb="FF56A31C"/>
-      <color rgb="FFEBD9FF"/>
       <color rgb="FFEEB500"/>
       <color rgb="FFFAFAFA"/>
       <color rgb="FFF2F2F2"/>
@@ -697,134 +725,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5835DB04-4600-40EA-8FAA-AA7BD16F57DC}">
-  <dimension ref="A1:Z28"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="16.5" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="48.125" style="1" customWidth="1"/>
-    <col min="3" max="26" width="7.625" customWidth="1"/>
+    <col min="3" max="21" width="7.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="69.75" customHeight="1">
-      <c r="A1" s="21"/>
-      <c r="B1" s="21"/>
-      <c r="C1" s="22" t="s">
+    <row r="1" spans="1:21" ht="36" customHeight="1">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
-      <c r="V1" s="22"/>
-      <c r="W1" s="22"/>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
-      <c r="Z1" s="22"/>
-    </row>
-    <row r="2" spans="1:26" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A2" s="10" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="11">
-        <v>46098</v>
-      </c>
-      <c r="D2" s="11">
-        <v>46099</v>
-      </c>
-      <c r="E2" s="11">
-        <v>46100</v>
-      </c>
-      <c r="F2" s="11">
-        <v>46101</v>
-      </c>
-      <c r="G2" s="11">
-        <v>46104</v>
-      </c>
-      <c r="H2" s="11">
-        <v>46105</v>
-      </c>
-      <c r="I2" s="11">
-        <v>46106</v>
-      </c>
-      <c r="J2" s="11">
-        <v>46107</v>
-      </c>
-      <c r="K2" s="11">
-        <v>46108</v>
-      </c>
-      <c r="L2" s="11">
-        <v>46111</v>
-      </c>
-      <c r="M2" s="11">
-        <v>46112</v>
-      </c>
-      <c r="N2" s="11">
-        <v>46113</v>
-      </c>
-      <c r="O2" s="11">
-        <v>46114</v>
-      </c>
-      <c r="P2" s="11">
-        <v>46115</v>
-      </c>
-      <c r="Q2" s="11">
-        <v>46118</v>
-      </c>
-      <c r="R2" s="11">
-        <v>46119</v>
-      </c>
-      <c r="S2" s="11">
-        <v>46120</v>
-      </c>
-      <c r="T2" s="11">
-        <v>46121</v>
-      </c>
-      <c r="U2" s="11">
-        <v>46122</v>
-      </c>
-      <c r="V2" s="11">
-        <v>46125</v>
-      </c>
-      <c r="W2" s="11">
-        <v>46126</v>
-      </c>
-      <c r="X2" s="11">
-        <v>46127</v>
-      </c>
-      <c r="Y2" s="11">
-        <v>46128</v>
-      </c>
-      <c r="Z2" s="11">
-        <v>46129</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" ht="35.25" customHeight="1" thickTop="1">
-      <c r="A3" s="23" t="s">
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="26" t="s">
         <v>3</v>
       </c>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="R1" s="24"/>
+      <c r="S1" s="24"/>
+      <c r="T1" s="24"/>
+      <c r="U1" s="25"/>
+    </row>
+    <row r="2" spans="1:21" ht="33" customHeight="1">
+      <c r="A2" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+    </row>
+    <row r="3" spans="1:21" ht="33" customHeight="1">
+      <c r="A3" s="19"/>
       <c r="B3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="4"/>
+        <v>8</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="3"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -841,22 +819,19 @@
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4"/>
-    </row>
-    <row r="4" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A4" s="23"/>
-      <c r="B4" s="8" t="s">
-        <v>5</v>
+    </row>
+    <row r="4" spans="1:21" ht="33" customHeight="1">
+      <c r="A4" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
@@ -871,26 +846,19 @@
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
-    </row>
-    <row r="5" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A5" s="19" t="s">
-        <v>6</v>
-      </c>
+    </row>
+    <row r="5" spans="1:21" ht="33" customHeight="1">
+      <c r="A5" s="20"/>
       <c r="B5" s="9" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="12"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -903,25 +871,20 @@
       <c r="S5" s="4"/>
       <c r="T5" s="4"/>
       <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
-    </row>
-    <row r="6" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A6" s="19"/>
+    </row>
+    <row r="6" spans="1:21" ht="33" customHeight="1">
+      <c r="A6" s="20"/>
       <c r="B6" s="9" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="12"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -933,26 +896,21 @@
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
       <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="4"/>
-    </row>
-    <row r="7" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A7" s="19"/>
-      <c r="B7" s="9" t="s">
-        <v>9</v>
+    </row>
+    <row r="7" spans="1:21" ht="33" customHeight="1">
+      <c r="A7" s="20"/>
+      <c r="B7" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="12"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
@@ -963,16 +921,11 @@
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
       <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
-      <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="4"/>
-      <c r="Z7" s="4"/>
-    </row>
-    <row r="8" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A8" s="19"/>
-      <c r="B8" s="16" t="s">
-        <v>10</v>
+    </row>
+    <row r="8" spans="1:21" ht="33" customHeight="1">
+      <c r="A8" s="20"/>
+      <c r="B8" s="13" t="s">
+        <v>14</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -980,10 +933,10 @@
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="12"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
@@ -993,16 +946,13 @@
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="4"/>
-      <c r="Z8" s="4"/>
-    </row>
-    <row r="9" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A9" s="19"/>
-      <c r="B9" s="16" t="s">
-        <v>11</v>
+    </row>
+    <row r="9" spans="1:21" ht="33" customHeight="1">
+      <c r="A9" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -1011,30 +961,23 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
-      <c r="Y9" s="4"/>
-      <c r="Z9" s="4"/>
-    </row>
-    <row r="10" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A10" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>13</v>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="12"/>
+    </row>
+    <row r="10" spans="1:21" ht="33" customHeight="1">
+      <c r="A10" s="21"/>
+      <c r="B10" s="11" t="s">
+        <v>17</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -1043,28 +986,23 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="6"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="12"/>
       <c r="M10" s="6"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="4"/>
-      <c r="Z10" s="4"/>
-    </row>
-    <row r="11" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A11" s="24"/>
-      <c r="B11" s="13" t="s">
-        <v>14</v>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="12"/>
+    </row>
+    <row r="11" spans="1:21" ht="33" customHeight="1">
+      <c r="A11" s="21"/>
+      <c r="B11" s="11" t="s">
+        <v>18</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -1075,26 +1013,21 @@
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
       <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="17"/>
-      <c r="T11" s="17"/>
-      <c r="U11" s="17"/>
-      <c r="V11" s="17"/>
-      <c r="W11" s="17"/>
-      <c r="X11" s="17"/>
-      <c r="Y11" s="17"/>
-      <c r="Z11" s="4"/>
-    </row>
-    <row r="12" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A12" s="24"/>
-      <c r="B12" s="13" t="s">
-        <v>15</v>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+      <c r="U11" s="12"/>
+    </row>
+    <row r="12" spans="1:21" ht="33" customHeight="1">
+      <c r="A12" s="21"/>
+      <c r="B12" s="15" t="s">
+        <v>19</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -1105,26 +1038,21 @@
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="17"/>
-      <c r="T12" s="17"/>
-      <c r="U12" s="17"/>
-      <c r="V12" s="17"/>
-      <c r="W12" s="17"/>
-      <c r="X12" s="17"/>
-      <c r="Y12" s="17"/>
-      <c r="Z12" s="4"/>
-    </row>
-    <row r="13" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A13" s="24"/>
-      <c r="B13" s="13" t="s">
-        <v>16</v>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+      <c r="U12" s="12"/>
+    </row>
+    <row r="13" spans="1:21" ht="33" customHeight="1">
+      <c r="A13" s="21"/>
+      <c r="B13" s="15" t="s">
+        <v>20</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -1135,26 +1063,23 @@
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="17"/>
-      <c r="T13" s="17"/>
-      <c r="U13" s="17"/>
-      <c r="V13" s="17"/>
-      <c r="W13" s="17"/>
-      <c r="X13" s="17"/>
-      <c r="Y13" s="17"/>
-      <c r="Z13" s="4"/>
-    </row>
-    <row r="14" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A14" s="24"/>
-      <c r="B14" s="14" t="s">
-        <v>17</v>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="12"/>
+    </row>
+    <row r="14" spans="1:21" ht="33" customHeight="1">
+      <c r="A14" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>22</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -1165,26 +1090,21 @@
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="17"/>
-      <c r="T14" s="17"/>
-      <c r="U14" s="17"/>
-      <c r="V14" s="17"/>
-      <c r="W14" s="17"/>
-      <c r="X14" s="17"/>
-      <c r="Y14" s="17"/>
-      <c r="Z14" s="4"/>
-    </row>
-    <row r="15" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A15" s="24"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="12"/>
+      <c r="U14" s="12"/>
+    </row>
+    <row r="15" spans="1:21" ht="33" customHeight="1">
+      <c r="A15" s="18"/>
       <c r="B15" s="14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -1195,28 +1115,21 @@
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="6"/>
-      <c r="T15" s="17"/>
-      <c r="U15" s="17"/>
-      <c r="V15" s="17"/>
-      <c r="W15" s="17"/>
-      <c r="X15" s="17"/>
-      <c r="Y15" s="17"/>
-      <c r="Z15" s="4"/>
-    </row>
-    <row r="16" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A16" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="27" t="s">
-        <v>20</v>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
+      <c r="U15" s="12"/>
+    </row>
+    <row r="16" spans="1:21" ht="33" customHeight="1">
+      <c r="A16" s="18"/>
+      <c r="B16" s="14" t="s">
+        <v>24</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -1227,26 +1140,21 @@
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="17"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="17"/>
-      <c r="V16" s="17"/>
-      <c r="W16" s="17"/>
-      <c r="X16" s="17"/>
-      <c r="Y16" s="17"/>
-      <c r="Z16" s="4"/>
-    </row>
-    <row r="17" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A17" s="20"/>
-      <c r="B17" s="15" t="s">
-        <v>21</v>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="12"/>
+      <c r="U16" s="12"/>
+    </row>
+    <row r="17" spans="1:21" ht="33" customHeight="1">
+      <c r="A17" s="18"/>
+      <c r="B17" s="14" t="s">
+        <v>25</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -1257,26 +1165,21 @@
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="17"/>
-      <c r="T17" s="17"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="17"/>
-      <c r="W17" s="17"/>
-      <c r="X17" s="17"/>
-      <c r="Y17" s="17"/>
-      <c r="Z17" s="4"/>
-    </row>
-    <row r="18" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A18" s="20"/>
-      <c r="B18" s="15" t="s">
-        <v>22</v>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="12"/>
+      <c r="R17" s="12"/>
+      <c r="S17" s="12"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="12"/>
+    </row>
+    <row r="18" spans="1:21" ht="33" customHeight="1">
+      <c r="A18" s="18"/>
+      <c r="B18" s="14" t="s">
+        <v>26</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -1287,150 +1190,67 @@
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="17"/>
-      <c r="S18" s="17"/>
-      <c r="T18" s="17"/>
-      <c r="U18" s="17"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="17"/>
-      <c r="X18" s="17"/>
-      <c r="Y18" s="17"/>
-      <c r="Z18" s="4"/>
-    </row>
-    <row r="19" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A19" s="20"/>
-      <c r="B19" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="17"/>
-      <c r="T19" s="17"/>
-      <c r="U19" s="17"/>
-      <c r="V19" s="17"/>
-      <c r="W19" s="7"/>
-      <c r="X19" s="17"/>
-      <c r="Y19" s="17"/>
-      <c r="Z19" s="4"/>
-    </row>
-    <row r="20" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A20" s="20"/>
-      <c r="B20" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
-      <c r="R20" s="17"/>
-      <c r="S20" s="17"/>
-      <c r="T20" s="17"/>
-      <c r="U20" s="17"/>
-      <c r="V20" s="17"/>
-      <c r="W20" s="17"/>
-      <c r="X20" s="7"/>
-      <c r="Y20" s="17"/>
-      <c r="Z20" s="4"/>
-    </row>
-    <row r="21" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A21" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4"/>
-      <c r="T21" s="4"/>
-      <c r="U21" s="4"/>
-      <c r="V21" s="4"/>
-      <c r="W21" s="4"/>
-      <c r="X21" s="4"/>
-      <c r="Y21" s="18"/>
-      <c r="Z21" s="18"/>
-    </row>
-    <row r="22" spans="1:26" hidden="1">
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="7"/>
+    </row>
+    <row r="19" spans="1:21" hidden="1">
+      <c r="A19" s="2"/>
+      <c r="B19" s="10"/>
+    </row>
+    <row r="20" spans="1:21" hidden="1">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+    </row>
+    <row r="21" spans="1:21" hidden="1">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22" spans="1:21" hidden="1">
       <c r="A22" s="2"/>
-      <c r="B22" s="12"/>
-    </row>
-    <row r="23" spans="1:26" hidden="1">
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23" spans="1:21" hidden="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
     </row>
-    <row r="24" spans="1:26" hidden="1">
+    <row r="24" spans="1:21" hidden="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
     </row>
-    <row r="25" spans="1:26" hidden="1">
+    <row r="25" spans="1:21" hidden="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
     </row>
-    <row r="26" spans="1:26" hidden="1">
+    <row r="26" spans="1:21" hidden="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
     </row>
-    <row r="27" spans="1:26" hidden="1">
+    <row r="27" spans="1:21" hidden="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
     </row>
-    <row r="28" spans="1:26" hidden="1">
+    <row r="28" spans="1:21" hidden="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A16:A20"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:Z1"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A9"/>
-    <mergeCell ref="A10:A15"/>
+  <mergeCells count="8">
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:K1"/>
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="Q1:U1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
